--- a/experiment/ELAN_bestx8/Test/results-Urban100/Urban100.xlsx
+++ b/experiment/ELAN_bestx8/Test/results-Urban100/Urban100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.91</v>
+        <v>24.82</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5286</v>
+        <v>0.6505</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.87</v>
+        <v>23.41</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4942</v>
+        <v>0.6339</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.24</v>
+        <v>21.49</v>
       </c>
       <c r="C4" t="n">
-        <v>0.394</v>
+        <v>0.4985</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.07</v>
+        <v>19.18</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4236</v>
+        <v>0.592</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.01</v>
+        <v>23.36</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6525</v>
+        <v>0.8531</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19.13</v>
+        <v>19.95</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3468</v>
+        <v>0.4389</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22.22</v>
+        <v>24.5</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.681</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18.04</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3079</v>
+        <v>0.4199</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28.41</v>
+        <v>30.24</v>
       </c>
       <c r="C10" t="n">
-        <v>0.725</v>
+        <v>0.8417</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.7</v>
+        <v>23.88</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6417</v>
+        <v>0.7919</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.73</v>
+        <v>14.93</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3851</v>
+        <v>0.5877</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20.87</v>
+        <v>22.01</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4596</v>
+        <v>0.5726</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23.52</v>
+        <v>26.06</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5435</v>
+        <v>0.7002</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20.17</v>
+        <v>20.91</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4534</v>
+        <v>0.5521</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20.85</v>
+        <v>23.09</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4594</v>
+        <v>0.6004</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22.52</v>
+        <v>25.97</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7093</v>
+        <v>0.8369</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21.1</v>
+        <v>22.5</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5463</v>
+        <v>0.6635</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22.41</v>
+        <v>23.95</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4364</v>
+        <v>0.5423</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16.8</v>
+        <v>18.32</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4743</v>
+        <v>0.6294999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.56</v>
+        <v>19.36</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4233</v>
+        <v>0.5201</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24.56</v>
+        <v>26.71</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5542</v>
+        <v>0.6796</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23.4</v>
+        <v>24.14</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5699</v>
+        <v>0.6485</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>22.41</v>
+        <v>24.44</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6094000000000001</v>
+        <v>0.7355</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>16.32</v>
+        <v>17.3</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2691</v>
+        <v>0.3849</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>22.93</v>
+        <v>27.57</v>
       </c>
       <c r="C26" t="n">
-        <v>0.627</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>23.9</v>
+        <v>25.56</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5183</v>
+        <v>0.6026</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>24.63</v>
+        <v>26</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5896</v>
+        <v>0.6873</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25.45</v>
+        <v>27.33</v>
       </c>
       <c r="C29" t="n">
-        <v>0.67</v>
+        <v>0.7838000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>20.82</v>
+        <v>23.29</v>
       </c>
       <c r="C30" t="n">
-        <v>0.553</v>
+        <v>0.7237</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.13</v>
+        <v>20.62</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4085</v>
+        <v>0.5647</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>20.93</v>
+        <v>21.73</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5348000000000001</v>
+        <v>0.6288</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>24.1</v>
+        <v>25.69</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6149</v>
+        <v>0.7266</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>22.43</v>
+        <v>24.54</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5454</v>
+        <v>0.6728</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>19.59</v>
+        <v>21.01</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3395</v>
+        <v>0.446</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>21.86</v>
+        <v>24.66</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5462</v>
+        <v>0.7318</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>22.24</v>
+        <v>24.76</v>
       </c>
       <c r="C37" t="n">
-        <v>0.6048</v>
+        <v>0.759</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>21.14</v>
+        <v>22.52</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4814</v>
+        <v>0.6004</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>23.16</v>
+        <v>24.37</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4026</v>
+        <v>0.4994</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>19.25</v>
+        <v>20.35</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4382</v>
+        <v>0.5537</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>16.05</v>
+        <v>19.78</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4453</v>
+        <v>0.7644</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>18.12</v>
+        <v>20.69</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4529</v>
+        <v>0.6793</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>21.76</v>
+        <v>23.94</v>
       </c>
       <c r="C43" t="n">
-        <v>0.5805</v>
+        <v>0.7304</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>18.67</v>
+        <v>25.76</v>
       </c>
       <c r="C44" t="n">
-        <v>0.5958</v>
+        <v>0.8397</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>22.89</v>
+        <v>25.88</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4763</v>
+        <v>0.6861</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>18.51</v>
+        <v>19.98</v>
       </c>
       <c r="C46" t="n">
-        <v>0.32</v>
+        <v>0.4117</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>21.51</v>
+        <v>22.17</v>
       </c>
       <c r="C47" t="n">
-        <v>0.5462</v>
+        <v>0.6463</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>18.45</v>
+        <v>19.51</v>
       </c>
       <c r="C48" t="n">
-        <v>0.4756</v>
+        <v>0.5986</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>16.32</v>
+        <v>16.85</v>
       </c>
       <c r="C49" t="n">
-        <v>0.5089</v>
+        <v>0.6153999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>18.01</v>
+        <v>19.95</v>
       </c>
       <c r="C50" t="n">
-        <v>0.3976</v>
+        <v>0.5481</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>21.78</v>
+        <v>22.66</v>
       </c>
       <c r="C51" t="n">
-        <v>0.5044</v>
+        <v>0.6108</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>22.24</v>
+        <v>23.7</v>
       </c>
       <c r="C52" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.6832</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>20.92</v>
+        <v>24.49</v>
       </c>
       <c r="C53" t="n">
-        <v>0.5504</v>
+        <v>0.7687</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>17.92</v>
+        <v>19.17</v>
       </c>
       <c r="C54" t="n">
-        <v>0.3948</v>
+        <v>0.5071</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>18.29</v>
+        <v>19.07</v>
       </c>
       <c r="C55" t="n">
-        <v>0.3673</v>
+        <v>0.4717</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>21.4</v>
+        <v>27.8</v>
       </c>
       <c r="C56" t="n">
-        <v>0.5755</v>
+        <v>0.8541</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>19.61</v>
+        <v>21.3</v>
       </c>
       <c r="C57" t="n">
-        <v>0.4274</v>
+        <v>0.5713</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>23.02</v>
+        <v>26.21</v>
       </c>
       <c r="C58" t="n">
-        <v>0.6405999999999999</v>
+        <v>0.7675999999999999</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>18.96</v>
+        <v>21.67</v>
       </c>
       <c r="C59" t="n">
-        <v>0.4987</v>
+        <v>0.668</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>19.52</v>
+        <v>20.23</v>
       </c>
       <c r="C60" t="n">
-        <v>0.5446</v>
+        <v>0.648</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>19.72</v>
+        <v>20.69</v>
       </c>
       <c r="C61" t="n">
-        <v>0.308</v>
+        <v>0.4067</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>20.66</v>
+        <v>21.34</v>
       </c>
       <c r="C62" t="n">
-        <v>0.4407</v>
+        <v>0.522</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>18.11</v>
+        <v>19.28</v>
       </c>
       <c r="C63" t="n">
-        <v>0.4855</v>
+        <v>0.6039</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>15.94</v>
+        <v>19.4</v>
       </c>
       <c r="C64" t="n">
-        <v>0.2834</v>
+        <v>0.487</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>21.87</v>
+        <v>22.95</v>
       </c>
       <c r="C65" t="n">
-        <v>0.5065</v>
+        <v>0.5913</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>21.46</v>
+        <v>22.29</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4002</v>
+        <v>0.4897</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>19.93</v>
+        <v>20.46</v>
       </c>
       <c r="C67" t="n">
-        <v>0.4105</v>
+        <v>0.4739</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>14.75</v>
+        <v>16.59</v>
       </c>
       <c r="C68" t="n">
-        <v>0.4973</v>
+        <v>0.7227</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>24.23</v>
+        <v>26.33</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5783</v>
+        <v>0.7124</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>21.04</v>
+        <v>22.37</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4708</v>
+        <v>0.5865</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>20.38</v>
+        <v>20.86</v>
       </c>
       <c r="C71" t="n">
-        <v>0.4132</v>
+        <v>0.4735</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>24.09</v>
+        <v>25.66</v>
       </c>
       <c r="C72" t="n">
-        <v>0.4332</v>
+        <v>0.5278</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>14.09</v>
+        <v>16.12</v>
       </c>
       <c r="C73" t="n">
-        <v>0.2956</v>
+        <v>0.5467</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>17.94</v>
+        <v>18.17</v>
       </c>
       <c r="C74" t="n">
-        <v>0.2426</v>
+        <v>0.2897</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>20.86</v>
+        <v>21.55</v>
       </c>
       <c r="C75" t="n">
-        <v>0.4262</v>
+        <v>0.5175</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>24.5</v>
+        <v>27.81</v>
       </c>
       <c r="C76" t="n">
-        <v>0.6703</v>
+        <v>0.8089</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>19.86</v>
+        <v>20.55</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4631</v>
+        <v>0.5432</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>20.69</v>
+        <v>21.27</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4623</v>
+        <v>0.5434</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>23.74</v>
+        <v>24.7</v>
       </c>
       <c r="C79" t="n">
-        <v>0.5376</v>
+        <v>0.6354</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>21.54</v>
+        <v>22.78</v>
       </c>
       <c r="C80" t="n">
-        <v>0.4235</v>
+        <v>0.5284</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>29.4</v>
+        <v>31.88</v>
       </c>
       <c r="C81" t="n">
-        <v>0.7804</v>
+        <v>0.9035</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>24.5</v>
+        <v>30.86</v>
       </c>
       <c r="C82" t="n">
-        <v>0.7443</v>
+        <v>0.9067</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>23.92</v>
+        <v>27.61</v>
       </c>
       <c r="C83" t="n">
-        <v>0.7214</v>
+        <v>0.8696</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>18.76</v>
+        <v>19.88</v>
       </c>
       <c r="C84" t="n">
-        <v>0.388</v>
+        <v>0.5043</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>23.63</v>
+        <v>25.09</v>
       </c>
       <c r="C85" t="n">
-        <v>0.5263</v>
+        <v>0.6331</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>22.88</v>
+        <v>24.16</v>
       </c>
       <c r="C86" t="n">
-        <v>0.6841</v>
+        <v>0.7857</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>24.69</v>
+        <v>25.35</v>
       </c>
       <c r="C87" t="n">
-        <v>0.6902</v>
+        <v>0.7952</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>20.47</v>
+        <v>23.59</v>
       </c>
       <c r="C88" t="n">
-        <v>0.5863</v>
+        <v>0.7544999999999999</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>17.06</v>
+        <v>17.82</v>
       </c>
       <c r="C89" t="n">
-        <v>0.2509</v>
+        <v>0.3437</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>23.36</v>
+        <v>24.46</v>
       </c>
       <c r="C90" t="n">
-        <v>0.4642</v>
+        <v>0.5584</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>26.86</v>
+        <v>31.19</v>
       </c>
       <c r="C91" t="n">
-        <v>0.7302999999999999</v>
+        <v>0.9127999999999999</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>19.98</v>
+        <v>21.26</v>
       </c>
       <c r="C92" t="n">
-        <v>0.3327</v>
+        <v>0.4581</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>15.49</v>
+        <v>16.18</v>
       </c>
       <c r="C93" t="n">
-        <v>0.3143</v>
+        <v>0.4188</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>19.71</v>
+        <v>21.76</v>
       </c>
       <c r="C94" t="n">
-        <v>0.5817</v>
+        <v>0.7187</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>23.39</v>
+        <v>24.78</v>
       </c>
       <c r="C95" t="n">
-        <v>0.5687</v>
+        <v>0.6681</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>17.63</v>
+        <v>18.39</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1605</v>
+        <v>0.2291</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>19.16</v>
+        <v>20.25</v>
       </c>
       <c r="C97" t="n">
-        <v>0.5115</v>
+        <v>0.6418</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>20.99</v>
+        <v>22.1</v>
       </c>
       <c r="C98" t="n">
-        <v>0.4693</v>
+        <v>0.5852000000000001</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>18.46</v>
+        <v>19.06</v>
       </c>
       <c r="C99" t="n">
-        <v>0.2519</v>
+        <v>0.3308</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>20.48</v>
+        <v>21.85</v>
       </c>
       <c r="C100" t="n">
-        <v>0.435</v>
+        <v>0.5314</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>19.65</v>
+        <v>23.03</v>
       </c>
       <c r="C101" t="n">
-        <v>0.4512</v>
+        <v>0.6012999999999999</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>20.81</v>
+        <v>22.62</v>
       </c>
       <c r="C102" t="n">
-        <v>0.4909</v>
+        <v>0.6207</v>
       </c>
     </row>
   </sheetData>
